--- a/02-Scraping-điều khiển trình duyệt/ket_qua_vjol.xlsx
+++ b/02-Scraping-điều khiển trình duyệt/ket_qua_vjol.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>machine learning; deep learning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>machine learning; deep learning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>machine learning; deep learning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>machine learning; deep learning</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>machine learning</t>
+          <t>machine learning; deep learning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1215,6 +1215,769 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>https://vjol.info.vn/tnu/vi/article/view/156848/133765</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Minimizing Flight Hours Losses by Utilizing Deep-Q Learning Techniques in Scheduling Aircraft Maintenance</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ha Manh Tuan</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Journal of Sciences and Technology - Smart Systems and Devices</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tập 34 Số 2 (2024)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Currently, there are insufficiently good or efficient tools or procedures for long-term scheduling of aviation maintenance activities in the world, and Vietnam specifically. Airlines are impacted by a variety of elements, including the quantity of aircraft they operate, their capacity, their personnel resources, their maintenance resources, and unforeseen and urgent occurrences that cause schedule disruptions. There are no fast, automatic solutions to the above-described problems existing in aviation today. The reinforcement learning method as described here could potentially be one answer to these problems. The idea is to plan in years running across a specified period such that the aircraft is brought as close as possible to the inspection deadline. From there, the airworthiness of the aircraft increases while the maintenance inspection decreases, reducing the cost of maintenance. Application optimization of the scheduling plan is done using the Deep Qlearning method. The results achieved by the Q-learning and Deep Q-learning algorithms are better in terms of computation times as compared to the other current techniques. The research results of the checks showed
+reinforcement learning potential in dealing with this problem, where the fly hours loss of planned inspections was reduced by using data from Vietnam Airlines. Computational experiments show that our methods adapt for different purposes and settings of reality. After teaching the model with these simulated conditions, they show how well a reinforcement learning application quickly arrives at lean repair plans.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/JST-SmartSystemsandDevices/vi/article/view/250559</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/JST-SmartSystemsandDevices/vi/article/view/250559/224130</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PHƯƠNG THỨC HỌC CẦN CÓ CHO SINH VIÊN Ở BẬC ĐẠI HỌC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Đỗ Thị Mỹ Trang; Đỗ Mạnh Cường; Đoàn Thị Huệ Dung</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Tạp chí Khoa học - Trường Đại học Sư phạm Hà Nội: Khoa học Giáo dục</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tập 4 Số 65 (2020)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Phương thức học sâu (cách học khám phá, hiểu bản chất của vấn đề) là phương thức học giúp sinh viên (SV) có năng lực vững chắc. Tuy nhiên, nhiều giảng viên (GV) nhận thấy SV hiện nay không quan tâm nhiều đến việc học, học thụ động, học đối phó cho qua môn. Đây thật sự là vấn đề mà nhiều GV đang quan tâm do bối cảnh xã hội hiện nay cần SV có cách học “chắc” (học sâu) để có khả năng phát triển nghề nghiệp. Vì vậy, mục tiêu của nghiên cứu này là phân tích làm rõ về phương thức học, đặc điểm của phương thức học sâu và những yếu tố ảnh hưởng. Từ đó, nghiên cứu đề xuất những định hướng trong thiết kế dạy học nhằm khuyến khích SV học sâu. Kết quả nghiên cứu cho thấy rằng phương thức học sâu được hình thành không chỉ bởi sử dụng các phương pháp dạy học tích cực (học trải nghiệm) mà còn phụ thuộc rất nhiều vào sự tổ chức, yêu cầu công việc, khuyến khích SV tư duy ở mức độ cao, v.v… từ người thầy. Ngoài ra, với cách học có phản biện cũng chính là yếu tố quan trọng giúp SV đạt được phương thức học sâu</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/DHSP-GD/vi/article/view/56657</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/DHSP-GD/vi/article/view/56657/47281</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NÂNG CAO HIỆU QUẢ ĐIỀU KHIỂN ROBOT, SỬ DỤNG HỌC TĂNG CƯỜNG KẾT HỢP HỌC SÂU</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lương Thị Thảo Hiếu; Phạm Thị Thùy; Nguyễn Khắc Hiệp</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Tạp chí Khoa học và Công nghệ - Đại học Thái Nguyên</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tập 228 Số 07 (2023): CÔNG NGHỆ THÔNG TIN VÀ TRUYỀN THÔNG</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tnu/vi/article/view/156806</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tnu/vi/article/view/156806/133727</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NÂNG CAO HIỆU QUẢ ĐIỀU KHIỂN ROBOT, SỬ DỤNG HỌC TĂNG CƯỜNG KẾT HỢP HỌC SÂU</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lương Thị Thảo Hiếu*, Phạm Thị Thùy, Nguyễn Khắc Hiệp</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Tạp chí Khoa học và Công nghệ - Đại học Thái Nguyên</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tập 228 Số 07 (2023): CÔNG NGHỆ THÔNG TIN VÀ TRUYỀN THÔNG</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Mặc dù học sâu có thể giải quyết các bài toán mà các thuật toán học máy cũ không giải quyết được nhưng cần lượng dữ liệu rất lớn và trong thực tế dữ liệu không phải lúc nào cũng có sẵn trong bài toán điều khiển. Học tăng cường là một giải pháp tốt trong bài toán điều khiển robot. Trong học tăng cường, dữ liệu được tạo ra khi tác tử tương tác với môi trường. Cùng với sự ra đời của mạng noron, nhiều nghiên cứu đã tập trung kết hợp mạng noron vào học tăng cường tạo nên học tăng cường sâu. Trong bài báo này chúng tôi đề xuất mô hình học tăng cường sâu mới dựa trên sự cải tiến thuật giải Deep Q Learning truyền thống bằng cách kết hợp các kỹ thuật: Fixed_Q Target, Double Deep Q, Prioritized Experience Replay, với mô hình mạng VGG16, ứng dụng điều khiển robot xếp hàng hóa với không gian trạng thái tự thiết kế sử dụng Unity ML-Agents.  Mô hình đề xuất được thực nghiệm, so sánh đánh giá hiệu quả so với mô hình ban đầu. Kết quả cho thấy phương pháp đề xuất hội tụ nhanh và khắc phục được hiện tượng ước lượng quá mức giá trị Q.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tnu/vi/article/view/81206</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tnu/vi/article/view/81206/69142</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ĐÁNH GIÁ PHƯƠNG THỨC HỌC CỦA SINH VIÊN TẠI TRƯỜNG ĐẠI HỌC SƯ PHẠM KỸ THUẬT TP.HCM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Đỗ Thị Mỹ Trang; Đỗ Mạnh Cường; Đoàn Thị Huệ Dung</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Tạp chí Khoa học - Trường Đại học Sư phạm Hà Nội: Khoa học Giáo dục</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tập 1 Số 66 (2021): Tháng 1.2021</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Học sâu (deep learning approaches - cách học khám phá, hiểu bản chất của vấn đề) là phương thức học cần có cho sinh viên (SV) đại học, bởi vì học sâu giúp SV có năng lực vững chắc. Tuy nhiên, nhiều SV hiện nay có cách học đối phó cho qua môn (học bề mặt), điều này dẫn đến năng lực của SV không đáp ứng được yêu cầu nghề nghiệp. Do đó, trong giảng dạy cần có sự điều chỉnh, định hướng SV có phương thức học (PTH) sâu. Để có cơ sở cho sự điều chỉnh, mục tiêu của nghiên cứu này là đánh giá phương thức học của SV và tìm ra các yếu tố ảnh hưởng. Thông qua khảo sát 653 SV tại trường ĐH Sư phạm kỹ thuật TP.HCM, dữ liệu được phân tích về độ tin cậy, thông số Mean, Phương sai, ANOVA, và phân tích dữ liệu định tính từ phỏng vấn sâu, kết quả nghiên cứu cho thấy SV có PTH sâu có chiến lược ở mức khá (Mean = 3.45). PTH bị ảnh hưởng bởi từ nhận thức của SV về tầm quan trọng của môn học, từ sự áp lực trong học tập, và từ sự mất tự tin ở bản thân SV. Từ đó, nghiên cứu cũng đã đề xuất các giải pháp trong thiết kế và tồ chức dạy học nhằm khuyến khích SV học sâu.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/DHSP-GD/vi/article/view/58065</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/DHSP-GD/vi/article/view/58065/49447</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Identify images of car collisions on the road using Deep Learning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thúy Nga</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Tạp chí Thiết bị Giáo dục</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Số 311 Kì 2 Tháng 4 (2024)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>An intelligent transportation system aims to steer vehicles without encountering accidents on the way to the destination. Autonomous vehicles greatly rely on cameras for perceiving their dynamically changing surroundings. Deep learning solutions to vision data is driving the research on collision mitigation systems for selfdriving cars or automobiles with a higher level of autonomy. This paper presents a three-class vehicular collision image classification dataset created from crowd-sourced dashboard camera videos containing on-road vehicular collisions. An image classification deep learning model is developed using teachable machine by transfer learning on the proposed dataset. The ability of the developed model to classify vehicular collision images based on the spatial aspect of the crash is evaluated and presented.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tctbgd/vi/article/view/96973</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tctbgd/vi/article/view/96973/81948</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>An Automated Deep Learning-Based Software for Total Lung Volume Calculation and Lung 3D Model Reconstruction</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tran Anh Vu</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Journal of Sciences and Technology - Smart Systems and Devices</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tập 33 Số 2 (2023)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>In this paper, we propose an automated deep learning-based software, especially for reconstructing 3D lung images and estimating Total Lung Volume (TLV). The system is mainly designed for Vietnamese users with Vietnamese as the default language. The purpose of our study is to build an automated system based on deep learning and machine-learning models to measure TLV and construct a 3D prototype of the lung. The training data is collected from The Cancer Imaging Archive (TCIA) dataset, provided by the 2017 Lung CT
+Segmentation Challenge for training and testing the proposed model. Our proposed system utilizes a modified Bi-directional Convolutional (ConvLSTM) U-Net (BCDU-Net) neural network. We use the lung segmentation results as the data to build 3D lung image and calculate the lung volume. We test the reliability of the software with real dataset collected from Bach Mai hospital. The overall results have shown that accuracy against actual data from commercial products is approximately 99% when using our model to calculate the TLV.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/JST-SmartSystemsandDevices/vi/article/view/249444</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/JST-SmartSystemsandDevices/vi/article/view/249444/223037</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tìm hiểu về một số phương pháp phát hiện ra Deepfake trong Deep learning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nguyễn Thu Huyền</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tạp chí Thiết bị Giáo dục</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Số 299 Kỳ 2 Tháng 10 (2023)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Deep Learning can be considered a subfield of Machine Learning– where computers learn and improve themselves through algorithms. It has been successfully applied to solve complex problems ranging from big data analytics to computer vision and human-level control. However, Deep Learning advances have also been used to create software that can pose threats to privacy, democracy, and national security. One of the new applications that has appeared recently is “Deepfakes”. Deepfake algorithms can create fake images and videos that humans cannot distinguish from real images or videos. Therefore, being able to detect and evaluate the correctness of images or videos is a current problem.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tctbgd/vi/article/view/90019</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tctbgd/vi/article/view/90019/76353</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A deep-learning model for semantic role labelling in medical documents</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tuấn Nguyên Hoài Đức; Trần Tiện Lợi Long Tứ; Lê Đình Việt Huy</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>VNUHCM Journal of Advanced Research in Natural Sciences (Tên cũ: Tạp chí Phát triển Khoa học &amp; Công nghệ: Khoa học Tự nhiên)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tập 5 Số 2 (2021)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>We built a model labelling the Predicate Argument Structure (PAS) for biomedical documents. PAS is an important semantic information of any document, because it reveals the main event mentioned in each sentence. Extracting PAS in a sentence is an important premise for the computer to solve a series of other problems related to the semantics in text such as event extraction, named entity extraction, question answering system… The predicate argument structure is domain dependent. Therefore, in Biomedical field, it is required to define a completely new Predicate Argument frame compared to the general field. For a machine learning model to work well with a new argument frame, identifying a new feature set is required. This is difficult, manual and requires a lot of expert labor. To address this challenge, we chose to train our model with Deep Learning method utilizing Bi-directional Long Short Term Memory. Deep learning is a machine learning method that does not require defining the feature sets manually. In addition, we also integrate Highway Connection between hidden neuron layers to minimize derivative loss. Besides, to overcome the problem of small training corpus, we integrate Deep Learning with Multi-task Learning technique. Multi-task Learning helps the main task (PAS tagging) to be complemented with knowledge learnt from a closely related task, the NER. Our model achieved F1 = 75.13% without any manually designed feature, thereby showing the prospect of Deep Learning in this domain. In addition, the experiment results also show that Multi-task Learning is an appropriate technique to overcome the problem of little training data in biomedical fields, by improving the F1 score.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/DHQGHCM-KNTN/vi/article/view/227071</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/DHQGHCM-KNTN/vi/article/view/227071/201120</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>KIỂM TRA ĐỘ MẠNH MẼ CỦA MÔ HÌNH HỌC SÂU BẰNG BA CUỘC TẤN CÔNG ĐỐI KHÁNG</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Trương Phi Hồ, Lê Thị Ngọc Ánh, Phan Xuân Khiêm, Phạm Duy Trung</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tạp chí Khoa học và Công nghệ - Đại học Thái Nguyên</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tập 228 Số 07 (2023): CÔNG NGHỆ THÔNG TIN VÀ TRUYỀN THÔNG</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Học sâu hiện đang là lĩnh vực được quan tâm nghiên cứu và phát triển bởi các nhà khoa học trên thế giới. Các mô hình học sâu được triển khai và ứng dụng nhiều trong thực tiễn phục vụ công việc và đời sống xã hội. Tuy nhiên học sâu lại tiềm tàng nhiều rủi ro có liên quan đến an toàn trong các ứng dụng, đặc biệt gần đây các cuộc tấn công sử dụng mẫu đối kháng đang là thách thức lớn đối với học sâu nói riêng và học máy nói chung. Để kiểm tra được độ mạnh mẽ của mô hình học máy, chúng tôi đề xuất sử dụng ba cuộc tấn công đối kháng để tính toán điểm chuẩn, các phương pháp tấn công thực nghiệm trên bộ dữ liệu MS-COCO đang được dùng để huấn luyện và kiểm tra đối với mô hình YOLO. Bài báo thống kê kết quả tỉ lệ tấn công thành công bằng các chỉ số đề xuất theo nghiên cứu thông qua quá trình thực nghiệm do nhóm tác giả thực hiện để kiểm chứng độ mạnh mẽ của mô hình học sâu nói chung. Các thực nghiệm toàn diện trong nghiên cứu được thực nghiệm trên mô hình YOLOv7 để kiểm tra và đánh giá độ mạnh mẽ của mô hình YOLOv7, đây cũng là mô hình học sâu đang được sử dụng phổ biến và được đánh giá là tiên tiến hiện nay.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tnu/vi/article/view/81209</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/tnu/vi/article/view/81209/69155</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>An overview of facial attribute learning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Phung Thai Thien Trang</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Tạp chí Khoa học - Trường Đại học Sư phạm TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tập 18 Số 3 (2021): Tap chí Khoa học</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Facial attributes are useful for developing applications such as face recognition, search, and surveillance. They are therefore important for various facial analysis. Many facial attribute learning algorithms have been developed to automatically detect those key attributes over the years. In this paper, we have surveyed some typical facial attribute learning methods. Five major categories of the state-of-the-art methods are identified: (1) Traditional learning, (2) Deep Single Task Learning, (3) Deep Multitask Learning, (4) Imbalanced Data Solver, and (5) Facial Attribute Ontology. They included from traditional learning algorithm to deep learning, along with methods that assist in solving semantic gaps based on ontology and solving data imbalances. For each algorithm of category, basic theories as well as their strengths, weaknesses, and differences are discussed. We also compared their performance on the standard datasets. Finally, based on characteristics and contribution of methods, we present conclusion and future works to solve facial attributes learning. The survey can help researchers gain a quick overview to build future human face applications as well as further studies.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/sphcm/vi/article/view/58052</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/sphcm/vi/article/view/58052/48476</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A Novel Method Forecasting for Big Data Analytics in Microgrid Energy Management</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Duong Minh Quan</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Journal of Sciences and Technology - Smart Systems and Devices</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tập 36 Số 1 (2026)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>With the rapid proliferation of renewable energy sources (RES) in modern power grids, the application of operational optimization strategies has become pivotal in maintaining system efficiency and stability. In particular, the hybrid deep learning model long short-term memory (LSTM) neural network combined with inductive conformal prediction (ICP) significantly enhances the accuracy of renewable energy forecasting and management. This paper presents the integration of big data analytics (BDA) with the LSTM+ICP framework for optimizing smart grid operations, particularly under real-time conditions. A suite of machine learning and deep learning models, especially the hybrid LSTM+ICP, is deployed to address critical challenges such as renewable output forecasting, load balancing, and fault detection. Owing to its capability to capture temporal dependencies and generate reliable prediction intervals, the LSTM+ICP model achieved a mean absolute percentage error (MAPE) of 2.91%, thus improving the reliability of renewable energy scheduling and enabling more efficient resource allocation. The implementation of real-time BDA in conjunction with LSTM+ICP reduced load variance by 44.3%, peak demand by 24.2%, and frequency deviations by 52.9%, thereby strengthening grid reliability and operational stability. In predictive maintenance, the LSTM+ICP model achieved a detection accuracy of 97.2% with an average lead time of 6.2 hours, enabling proactive interventions and minimizing fault risks. For system optimization, the application of reinforcement learning augmented by BDA led to a 33.9% reduction in power losses, a 22.4% increase in voltage stability, and a 29.1% decrease in reactive power, thereby enhancing operational efficiency. From both economic and environmental perspectives, the BDA-driven approach resulted in monthly cost savings of C36,150 and a 30.2% reduction in CO2 emissions, demonstrating the efficacy and sustainability of the proposed methodology.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/JST-SmartSystemsandDevices/vi/article/view/252058</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/JST-SmartSystemsandDevices/vi/article/view/252058/225581</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Exploiting Deep Reinforcement Learning for Coverage Maximization and Cost Minimization in Air Quality Monitoring Systems</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Nguyen Thanh Hung</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Journal of Sciences and Technology - Smart Systems and Devices</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tập 32 Số 3 (2022)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2022-09-15</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Air-quality monitoring is highly desired in modern life, where environmental problems have become more serious. Such a task requires continuous surveillance over large urban areas, which is costly both in infrastructure and sensor resources. Hence it gives rise to Vehicular Mobile Networks (VMNs), in which mobile vehicles play the role of sensor devices and constantly monitor the area. However, with extensive constraints, the optimization of both maximizing the coverage and minimizing the sensory costs is vastly challenging. In this research, we resolve the problem in terms of a learning process. Applying deep reinforcement learning, we outperform more than 1.65% in terms of coverage, compared to common setups while remaining considerably small sensory costs in terms of sensor activation rate. We conduct extensive experiments for a better understanding of the behavior of the deep reinforcement learning model.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/JST-SmartSystemsandDevices/vi/article/view/249363</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/JST-SmartSystemsandDevices/vi/article/view/249363/222958</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Deep Reinforcement Learning with Hidden Markov Model for Speech Recognition</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Samson Isaac; Khalid Haruna; Muhammad Aminu Ahmad; Rabi Mustapha</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Journal of Technology &amp; Innovation (JTIN)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tập 3 Số 1 (2023)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Nowadays, many applications uses speech recognition especially the field of computer science and electronics, Speech Recognition (SR) is the interpretation of words spoken into a text. It is also known as Speech-To-Text (STT) or Automatic-Speech-Recognition(ASR), or just Word-Recognition(WR). The Hidden-Markov-Model (HMM) is a type of Markov model, which means that the future state of the model depends on the current state, not on the entire history of the system and the goal of HMM is to learn a sequence of hidden states from a set of known states. The Long-Short-Time-Memory (LSTM) network is a type of Recurrent Neural Network (RNN) that can learn long-term dependencies between time steps of sequence data. The LSTM network is trained by the network in order to predict the values of subsequent time steps in a series-to-series regression. Deep Neural Network (DNN) models are better classifiers than Gaussian Mixture Models (GMMs), they can generalize much better with a smaller number of parameters over complex distributions. They model distributions of different classes jointly, called “distributed” learning, or, more properly “tied” learning. This work is aimed at developing a speech recognition model that will predict isolated speech of some selected fruits in Hausa, Igbo and Yoruba language by using the predicting power of Mel-Frequency-Cepstral-Coefficient (MFCC), LSTM and HMM algorithms. The findings of the study would improve the development of better automatic speech applications systems and would benefit the academic and research community in the field of Natural Language Processing.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/TCKHCNST/vi/article/view/83877</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/TCKHCNST/vi/article/view/83877/71414</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>deep learning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Relationship between learning attitude, self-efficacy, and caring behavior among nursing students in selected universities in Vietnam</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Nguyen Hong Thiep, Edreck D. Estioko</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Tạp chí Khoa học Điều dưỡng</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tập 9 Số 01 (Số TA) (2026): Tạp chí Khoa học Điều dưỡng</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Objectives: This study aims to examine the relationship between learning attitude, self-efficacy, and caring behavior among undergraduate nursing students in three selected public universities in Vietnam. Methods:A descriptive-correlational design was used with 428 nursing students from three public universities in southern Vietnam from December 2024 to February 2025. Standardized instruments were applied, including the R-SPQ-2F for learning attitudes, the Self-Efficacy for Learning and Performance Scale, and the Caring Behaviors Inventory (CBI-24). All tools were translated and culturally adapted for Vietnamese participants. Data analysis employed descriptive statistics, Pearson’s correlation, and regression modeling. Results: Results showed moderate surface (M = 2.71, SD = 0.831 ) and deep (M = 3.32, SD = 0.7) learning approaches. Self-efficacy was rated as good in both self-learning (M = 2.63, SD = 0.48) and self-performance (M = 2.98, SD = 0.396). Caring behavior was consistently high across all domains, including being with (M = 4.85, SD = 0.746), doing with competence (M = 4.88, SD = 0.81), responding to needs (M = 5.01, SD = 0.81), and providing effective care (M = 4.89, SD = 0.942). Deep learning attitude was positively correlated with self-efficacy (r = 0.195–0.204, p &lt; 0.001) and all caring behavior dimensions (r = 0.183–0.204, p &lt; 0.001). Self-efficacy also correlated positively with caring behavior in both learning (r = 0.135–0.156) and performance domains (r = 0.135–0.165). Regression analysis confirmed a significant direct effect of self-efficacy on caring behavior (β = 0.3152, p &lt; 0.001) and a smaller indirect effect mediated by learning attitude (estimate = 0.0378, p = 0.041), indicating partial mediation. Conclusion: The findings highlight the importance of strengthening self-efficacy and fostering deep learning approaches to enhance compassionate and competent nursing care. Future research should design interventions that integrate these elements into nursing curricula</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/DHDDND/vi/article/view/138506</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://vjol.info.vn/DHDDND/vi/article/view/138506/113167</t>
         </is>
       </c>
     </row>
